--- a/Estudio_Economico_Agentes.xlsx
+++ b/Estudio_Economico_Agentes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex_\Desktop\Proyecto MItumi\mitumi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E3813C-76DC-4A3C-AB25-78A9EE5A21F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5B1B9C4-385B-45B9-BDEB-3FAFA1293081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" tabRatio="500" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Configuración" sheetId="1" r:id="rId1"/>
@@ -406,7 +406,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="#,##0&quot; €&quot;"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -474,6 +474,14 @@
       <sz val="11"/>
       <name val="Cambria"/>
       <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -582,31 +590,31 @@
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4559,10 +4567,10 @@
                 <c:formatCode>#,##0.00" €"</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>330</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3960</c:v>
+                  <c:v>3000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5361,7 +5369,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -5494,9 +5502,6 @@
       <c r="D9" s="9">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="C16" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6000,7 +6005,7 @@
       </c>
     </row>
     <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="12" t="s">
         <v>24</v>
       </c>
       <c r="B11" s="13"/>
@@ -6574,7 +6579,7 @@
       </c>
     </row>
     <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="14" t="s">
         <v>24</v>
       </c>
       <c r="B11" s="13"/>
@@ -6665,7 +6670,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -6709,11 +6714,11 @@
         <v>0</v>
       </c>
       <c r="C3" s="4">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D3" s="4">
         <f t="shared" si="0"/>
-        <v>720</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -6723,12 +6728,10 @@
       <c r="B4" s="4">
         <v>0</v>
       </c>
-      <c r="C4" s="4">
-        <v>30</v>
-      </c>
+      <c r="C4" s="4"/>
       <c r="D4" s="4">
         <f t="shared" si="0"/>
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -6739,11 +6742,11 @@
         <v>0</v>
       </c>
       <c r="C5" s="4">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D5" s="4">
         <f t="shared" si="0"/>
-        <v>180</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -6751,7 +6754,7 @@
         <v>62</v>
       </c>
       <c r="B6" s="4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C6" s="4">
         <v>0</v>
@@ -6827,16 +6830,19 @@
       </c>
       <c r="B11" s="4">
         <f>SUM(B2:B10)</f>
-        <v>8020</v>
+        <v>8015</v>
       </c>
       <c r="C11" s="4">
         <f>SUM(C2:C10)</f>
-        <v>330</v>
+        <v>250</v>
       </c>
       <c r="D11" s="4">
         <f>SUM(D2:D10)</f>
-        <v>3960</v>
-      </c>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D16" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6957,7 +6963,7 @@
         <f t="shared" si="0"/>
         <v>266</v>
       </c>
-      <c r="K3" s="25" t="s">
+      <c r="K3" s="15" t="s">
         <v>78</v>
       </c>
       <c r="L3" s="13"/>
@@ -8052,7 +8058,7 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="15" t="s">
         <v>97</v>
       </c>
       <c r="B10" s="13"/>
@@ -8161,7 +8167,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="25" t="s">
+      <c r="A20" s="15" t="s">
         <v>99</v>
       </c>
       <c r="B20" s="13"/>
@@ -8270,7 +8276,7 @@
       </c>
     </row>
     <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="25" t="s">
+      <c r="A30" s="15" t="s">
         <v>100</v>
       </c>
       <c r="B30" s="13"/>
@@ -8379,7 +8385,7 @@
       </c>
     </row>
     <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="25" t="s">
+      <c r="A40" s="15" t="s">
         <v>101</v>
       </c>
       <c r="B40" s="13"/>
@@ -8517,7 +8523,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="25" t="s">
         <v>102</v>
       </c>
       <c r="B1" s="13"/>
@@ -8539,147 +8545,147 @@
       <c r="H2" s="13"/>
     </row>
     <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="18" t="s">
+      <c r="B4" s="18"/>
+      <c r="C4" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="18" t="s">
+      <c r="D4" s="18"/>
+      <c r="E4" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="F4" s="19"/>
-      <c r="G4" s="18" t="s">
+      <c r="F4" s="18"/>
+      <c r="G4" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="H4" s="19"/>
+      <c r="H4" s="18"/>
     </row>
     <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14">
+      <c r="A5" s="17">
         <f>Agentes!O9+Despliegue!C11</f>
-        <v>336.03492</v>
-      </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="14">
+        <v>256.03492</v>
+      </c>
+      <c r="B5" s="19"/>
+      <c r="C5" s="17">
         <f>Agentes!P9+Despliegue!D11</f>
-        <v>4032.4190399999998</v>
-      </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="21">
+        <v>3072.4190399999998</v>
+      </c>
+      <c r="D5" s="19"/>
+      <c r="E5" s="24">
         <f>COUNTA(Agentes!A2:A8)</f>
         <v>6</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="14">
+      <c r="F5" s="19"/>
+      <c r="G5" s="17">
         <f>Agentes!O9/COUNTA(Agentes!A2:A8)</f>
         <v>1.0058200000000002</v>
       </c>
-      <c r="H5" s="15"/>
+      <c r="H5" s="19"/>
     </row>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="16"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="21"/>
     </row>
     <row r="7" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="18" t="s">
+      <c r="B7" s="18"/>
+      <c r="C7" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="D7" s="19"/>
-      <c r="E7" s="18" t="s">
+      <c r="D7" s="18"/>
+      <c r="E7" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="F7" s="19"/>
-      <c r="G7" s="18" t="s">
+      <c r="F7" s="18"/>
+      <c r="G7" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="H7" s="19"/>
+      <c r="H7" s="18"/>
     </row>
     <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="str">
+      <c r="A8" s="22" t="str">
         <f>INDEX(Agentes!A2:A8,MATCH(MAX(Agentes!O2:O8),Agentes!O2:O8,0))</f>
         <v>Lumen (consultas)</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="20" t="str">
+      <c r="B8" s="19"/>
+      <c r="C8" s="22" t="str">
         <f>INDEX(Agentes!A2:A8,MATCH(MIN(Agentes!O2:O8),Agentes!O2:O8,0))</f>
         <v>Vigil (concursos)</v>
       </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="14">
+      <c r="D8" s="19"/>
+      <c r="E8" s="17">
         <f>Agentes!O9</f>
         <v>6.0349200000000005</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="14">
+      <c r="F8" s="19"/>
+      <c r="G8" s="17">
         <f>Despliegue!C11</f>
-        <v>330</v>
-      </c>
-      <c r="H8" s="15"/>
+        <v>250</v>
+      </c>
+      <c r="H8" s="19"/>
     </row>
     <row r="9" spans="1:8" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="16"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="17"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="21"/>
     </row>
     <row r="10" spans="1:8" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="18" t="s">
+      <c r="B10" s="18"/>
+      <c r="C10" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D10" s="19"/>
-      <c r="E10" s="18" t="s">
+      <c r="D10" s="18"/>
+      <c r="E10" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="F10" s="19"/>
-      <c r="G10" s="18" t="s">
+      <c r="F10" s="18"/>
+      <c r="G10" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="H10" s="19"/>
+      <c r="H10" s="18"/>
     </row>
     <row r="11" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="14">
+      <c r="A11" s="17">
         <f>Despliegue!B11</f>
-        <v>8020</v>
-      </c>
-      <c r="B11" s="19"/>
-      <c r="C11" s="14">
+        <v>8015</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="C11" s="17">
         <f>Despliegue!D11</f>
-        <v>3960</v>
-      </c>
-      <c r="D11" s="19"/>
-      <c r="E11" s="14">
+        <v>3000</v>
+      </c>
+      <c r="D11" s="18"/>
+      <c r="E11" s="17">
         <f>Agentes!P9+Despliegue!B11+Despliegue!D11</f>
-        <v>12052.419040000001</v>
-      </c>
-      <c r="F11" s="19"/>
-      <c r="G11" s="14">
+        <v>11087.419040000001</v>
+      </c>
+      <c r="F11" s="18"/>
+      <c r="G11" s="17">
         <f>Agentes!B18+Despliegue!D11</f>
-        <v>4060.7710941599998</v>
-      </c>
-      <c r="H11" s="19"/>
+        <v>3100.7710941599998</v>
+      </c>
+      <c r="H11" s="18"/>
     </row>
     <row r="46" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="22" t="s">
+      <c r="A46" s="16" t="s">
         <v>115</v>
       </c>
       <c r="B46" s="13"/>
@@ -8706,7 +8712,7 @@
       </c>
       <c r="C48" s="4">
         <f>Despliegue!C11</f>
-        <v>330</v>
+        <v>250</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -8719,11 +8725,21 @@
       </c>
       <c r="C49" s="4">
         <f>Despliegue!D11</f>
-        <v>3960</v>
+        <v>3000</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="G8:H9"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C8:D9"/>
+    <mergeCell ref="E4:F4"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="G11:H11"/>
@@ -8740,16 +8756,6 @@
     <mergeCell ref="C5:D6"/>
     <mergeCell ref="E5:F6"/>
     <mergeCell ref="E8:F9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="G8:H9"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C8:D9"/>
-    <mergeCell ref="E4:F4"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
